--- a/outputs/lcr_acceptance_20260720/LCR验收测量记录.xlsx
+++ b/outputs/lcr_acceptance_20260720/LCR验收测量记录.xlsx
@@ -995,14 +995,26 @@
       <c r="E20" t="str">
         <v>无</v>
       </c>
+      <c r="F20" t="str">
+        <v>6.7</v>
+      </c>
       <c r="G20" t="str">
         <v/>
       </c>
+      <c r="H20" t="str">
+        <v>50k</v>
+      </c>
       <c r="I20" t="str">
         <v>串联</v>
       </c>
+      <c r="J20" t="str">
+        <v>1.926</v>
+      </c>
+      <c r="K20" t="str">
+        <v>2.105</v>
+      </c>
       <c r="L20" t="str">
-        <v>无器材</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1047,14 +1059,26 @@
       <c r="E22" t="str">
         <v>无</v>
       </c>
+      <c r="F22" t="str">
+        <v>17.329</v>
+      </c>
       <c r="G22" t="str">
         <v/>
       </c>
+      <c r="H22" t="str">
+        <v>50k</v>
+      </c>
       <c r="I22" t="str">
         <v>串联</v>
       </c>
+      <c r="J22" t="str">
+        <v>2.292</v>
+      </c>
+      <c r="K22" t="str">
+        <v>5.444</v>
+      </c>
       <c r="L22" t="str">
-        <v>无器材</v>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1073,14 +1097,26 @@
       <c r="E23" t="str">
         <v>无</v>
       </c>
+      <c r="F23" t="str">
+        <v>36.055</v>
+      </c>
       <c r="G23" t="str">
         <v/>
       </c>
+      <c r="H23" t="str">
+        <v>50k</v>
+      </c>
       <c r="I23" t="str">
         <v>串联</v>
       </c>
+      <c r="J23" t="str">
+        <v>2.114</v>
+      </c>
+      <c r="K23" t="str">
+        <v>11.327</v>
+      </c>
       <c r="L23" t="str">
-        <v>无器材</v>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -1099,14 +1135,26 @@
       <c r="E24" t="str">
         <v>无</v>
       </c>
+      <c r="F24" t="str">
+        <v>46.846</v>
+      </c>
       <c r="G24" t="str">
         <v/>
       </c>
+      <c r="H24" t="str">
+        <v>50k</v>
+      </c>
       <c r="I24" t="str">
         <v>串联</v>
       </c>
+      <c r="J24" t="str">
+        <v>3.026</v>
+      </c>
+      <c r="K24" t="str">
+        <v>14.717</v>
+      </c>
       <c r="L24" t="str">
-        <v>无器材</v>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -1151,14 +1199,23 @@
       <c r="E26" t="str">
         <v>无</v>
       </c>
+      <c r="F26" t="str">
+        <v>85.409</v>
+      </c>
       <c r="G26" t="str">
         <v/>
       </c>
+      <c r="H26" t="str">
+        <v>50k</v>
+      </c>
       <c r="I26" t="str">
         <v>串联</v>
       </c>
-      <c r="L26" t="str">
-        <v>无器材</v>
+      <c r="J26" t="str">
+        <v>5.268</v>
+      </c>
+      <c r="K26" t="str">
+        <v>26.832</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/lcr_acceptance_20260720/LCR验收测量记录.xlsx
+++ b/outputs/lcr_acceptance_20260720/LCR验收测量记录.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:M26"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -479,6 +479,9 @@
       <c r="L5" t="str">
         <v>备注</v>
       </c>
+      <c r="M5" t="str">
+        <v>反馈档位（VIR）</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -497,7 +500,7 @@
         <v>20.2</v>
       </c>
       <c r="F6" t="str">
-        <v>20.169</v>
+        <v>19.277</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -509,10 +512,13 @@
         <v>串联</v>
       </c>
       <c r="J6" t="str">
-        <v>20.169</v>
+        <v>19.277</v>
       </c>
       <c r="K6" t="str">
-        <v>0.161</v>
+        <v>0.089</v>
+      </c>
+      <c r="M6" t="str">
+        <v>4、1、100</v>
       </c>
     </row>
     <row r="7">
@@ -532,7 +538,7 @@
         <v>99.6</v>
       </c>
       <c r="F7" t="str">
-        <v>100.751</v>
+        <v>97.661</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -544,10 +550,13 @@
         <v>串联</v>
       </c>
       <c r="J7" t="str">
-        <v>100.751</v>
+        <v>97.661</v>
       </c>
       <c r="K7" t="str">
-        <v>1.698</v>
+        <v>1.203</v>
+      </c>
+      <c r="M7" t="str">
+        <v>1、1、100</v>
       </c>
     </row>
     <row r="8">
@@ -567,7 +576,7 @@
         <v>1.194k</v>
       </c>
       <c r="F8" t="str">
-        <v>1.194k</v>
+        <v>1.185k</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -579,10 +588,13 @@
         <v>串联</v>
       </c>
       <c r="J8" t="str">
-        <v>1.194k</v>
+        <v>1.185k</v>
       </c>
       <c r="K8" t="str">
-        <v>27.643</v>
+        <v>27.227</v>
+      </c>
+      <c r="M8" t="str">
+        <v>1、8、100</v>
       </c>
     </row>
     <row r="9">
@@ -602,22 +614,25 @@
         <v>10.0k</v>
       </c>
       <c r="F9" t="str">
-        <v>9.982k</v>
+        <v>10.011k</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>1？k</v>
+        <v>1k</v>
       </c>
       <c r="I9" t="str">
         <v>串联</v>
       </c>
       <c r="J9" t="str">
-        <v>9.982k</v>
+        <v>10.011k</v>
       </c>
       <c r="K9" t="str">
-        <v>1.120k</v>
+        <v>1.085k</v>
+      </c>
+      <c r="M9" t="str">
+        <v>1、64、100</v>
       </c>
     </row>
     <row r="10">
@@ -637,7 +652,7 @@
         <v>39.7k</v>
       </c>
       <c r="F10" t="str">
-        <v>40.838k</v>
+        <v>38.009k</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -649,10 +664,13 @@
         <v>串联</v>
       </c>
       <c r="J10" t="str">
-        <v>40.838k</v>
+        <v>38.009k</v>
       </c>
       <c r="K10" t="str">
-        <v>1.885k</v>
+        <v>-349.404</v>
+      </c>
+      <c r="M10" t="str">
+        <v>1、4、100k</v>
       </c>
     </row>
     <row r="11">
@@ -672,7 +690,7 @@
         <v>67.0k</v>
       </c>
       <c r="F11" t="str">
-        <v>69.732k</v>
+        <v>63.959k</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -684,10 +702,13 @@
         <v>串联</v>
       </c>
       <c r="J11" t="str">
-        <v>69.732k</v>
+        <v>63.959k</v>
       </c>
       <c r="K11" t="str">
-        <v>2.615k</v>
+        <v>-992.896</v>
+      </c>
+      <c r="M11" t="str">
+        <v>1、8、100k</v>
       </c>
     </row>
     <row r="12">
@@ -707,7 +728,7 @@
         <v>93.9k</v>
       </c>
       <c r="F12" t="str">
-        <v>97.384k</v>
+        <v>89.378k</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -719,10 +740,13 @@
         <v>串联</v>
       </c>
       <c r="J12" t="str">
-        <v>97.384k</v>
+        <v>89.378k</v>
       </c>
       <c r="K12" t="str">
-        <v>7.884k</v>
+        <v>-2.380kk</v>
+      </c>
+      <c r="M12" t="str">
+        <v>1、8、100k</v>
       </c>
     </row>
     <row r="13">
@@ -742,7 +766,7 @@
         <v>无</v>
       </c>
       <c r="F13" t="str">
-        <v>0.888</v>
+        <v>0.894</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -754,13 +778,16 @@
         <v>串联</v>
       </c>
       <c r="J13" t="str">
-        <v>3.856k</v>
+        <v>3.845k</v>
       </c>
       <c r="K13" t="str">
-        <v>-17.920k</v>
+        <v>-17.793k</v>
       </c>
       <c r="L13" t="str">
         <v/>
+      </c>
+      <c r="M13" t="str">
+        <v>1、128、100</v>
       </c>
     </row>
     <row r="14">
@@ -780,7 +807,7 @@
         <v>无</v>
       </c>
       <c r="F14" t="str">
-        <v>10.371</v>
+        <v>10.823</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -792,13 +819,16 @@
         <v>串联</v>
       </c>
       <c r="J14" t="str">
-        <v>7.859</v>
+        <v>15.204</v>
       </c>
       <c r="K14" t="str">
-        <v>-1.534k</v>
+        <v>-1.470k</v>
       </c>
       <c r="L14" t="str">
         <v/>
+      </c>
+      <c r="M14" t="str">
+        <v>1、8、100</v>
       </c>
     </row>
     <row r="15">
@@ -818,7 +848,7 @@
         <v>无</v>
       </c>
       <c r="F15" t="str">
-        <v>88.512</v>
+        <v>94.283</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -830,13 +860,16 @@
         <v>串联</v>
       </c>
       <c r="J15" t="str">
-        <v>2.249</v>
+        <v>2.117</v>
       </c>
       <c r="K15" t="str">
-        <v>-179.811</v>
+        <v>-168.805</v>
       </c>
       <c r="L15" t="str">
         <v/>
+      </c>
+      <c r="M15" t="str">
+        <v>1、1、100</v>
       </c>
     </row>
     <row r="16">
@@ -856,7 +889,7 @@
         <v>无</v>
       </c>
       <c r="F16" t="str">
-        <v>228.651</v>
+        <v>237.403</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -868,10 +901,13 @@
         <v>串联</v>
       </c>
       <c r="J16" t="str">
-        <v>2.061</v>
+        <v>1.417</v>
       </c>
       <c r="K16" t="str">
-        <v>-69.606</v>
+        <v>-67.040</v>
+      </c>
+      <c r="M16" t="str">
+        <v>1、1、100</v>
       </c>
     </row>
     <row r="17">
@@ -891,7 +927,7 @@
         <v>无</v>
       </c>
       <c r="F17" t="str">
-        <v>448.817</v>
+        <v>455.132</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -903,10 +939,13 @@
         <v>串联</v>
       </c>
       <c r="J17" t="str">
-        <v>0.937</v>
+        <v>0.556</v>
       </c>
       <c r="K17" t="str">
-        <v>-35.461</v>
+        <v>-34.969</v>
+      </c>
+      <c r="M17" t="str">
+        <v>2、1、100</v>
       </c>
     </row>
     <row r="18">
@@ -926,7 +965,7 @@
         <v>无</v>
       </c>
       <c r="F18" t="str">
-        <v>871.175</v>
+        <v>890.826</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -938,10 +977,13 @@
         <v>串联</v>
       </c>
       <c r="J18" t="str">
-        <v>0.418</v>
+        <v>0.297</v>
       </c>
       <c r="K18" t="str">
-        <v>-18.269</v>
+        <v>-17.866</v>
+      </c>
+      <c r="M18" t="str">
+        <v>4、1、100</v>
       </c>
     </row>
     <row r="19">
@@ -961,7 +1003,7 @@
         <v>无</v>
       </c>
       <c r="F19" t="str">
-        <v>4223</v>
+        <v>4264</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -973,10 +1015,13 @@
         <v>串联</v>
       </c>
       <c r="J19" t="str">
-        <v>0.012</v>
+        <v>0.065</v>
       </c>
       <c r="K19" t="str">
-        <v>-3.768</v>
+        <v>-3.732</v>
+      </c>
+      <c r="M19" t="str">
+        <v>16、1、100</v>
       </c>
     </row>
     <row r="20">
@@ -996,7 +1041,7 @@
         <v>无</v>
       </c>
       <c r="F20" t="str">
-        <v>6.7</v>
+        <v>6.541</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1011,10 +1056,13 @@
         <v>1.926</v>
       </c>
       <c r="K20" t="str">
-        <v>2.105</v>
+        <v>2.055</v>
       </c>
       <c r="L20" t="str">
-        <v/>
+        <v>电感测量明显比前二者慢，应该是跳成50k的原因</v>
+      </c>
+      <c r="M20" t="str">
+        <v>64、2、100</v>
       </c>
     </row>
     <row r="21">
@@ -1060,7 +1108,7 @@
         <v>无</v>
       </c>
       <c r="F22" t="str">
-        <v>17.329</v>
+        <v>21.967</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1072,13 +1120,16 @@
         <v>串联</v>
       </c>
       <c r="J22" t="str">
-        <v>2.292</v>
+        <v>2.298</v>
       </c>
       <c r="K22" t="str">
-        <v>5.444</v>
+        <v>6.901</v>
       </c>
       <c r="L22" t="str">
         <v/>
+      </c>
+      <c r="M22" t="str">
+        <v>32、2、100</v>
       </c>
     </row>
     <row r="23">
@@ -1098,7 +1149,7 @@
         <v>无</v>
       </c>
       <c r="F23" t="str">
-        <v>36.055</v>
+        <v>34.995</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1110,13 +1161,16 @@
         <v>串联</v>
       </c>
       <c r="J23" t="str">
-        <v>2.114</v>
+        <v>3.268</v>
       </c>
       <c r="K23" t="str">
-        <v>11.327</v>
+        <v>10.994</v>
       </c>
       <c r="L23" t="str">
         <v/>
+      </c>
+      <c r="M23" t="str">
+        <v>32、2、100</v>
       </c>
     </row>
     <row r="24">
@@ -1136,7 +1190,7 @@
         <v>无</v>
       </c>
       <c r="F24" t="str">
-        <v>46.846</v>
+        <v>46.591</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1148,13 +1202,16 @@
         <v>串联</v>
       </c>
       <c r="J24" t="str">
-        <v>3.026</v>
+        <v>3.130</v>
       </c>
       <c r="K24" t="str">
-        <v>14.717</v>
+        <v>14.637</v>
       </c>
       <c r="L24" t="str">
         <v/>
+      </c>
+      <c r="M24" t="str">
+        <v>16、2、100</v>
       </c>
     </row>
     <row r="25">
@@ -1200,7 +1257,7 @@
         <v>无</v>
       </c>
       <c r="F26" t="str">
-        <v>85.409</v>
+        <v>94.812</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1212,15 +1269,18 @@
         <v>串联</v>
       </c>
       <c r="J26" t="str">
-        <v>5.268</v>
+        <v>5.108</v>
       </c>
       <c r="K26" t="str">
-        <v>26.832</v>
+        <v>29.786</v>
+      </c>
+      <c r="M26" t="str">
+        <v>8、2、100</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M26"/>
   </ignoredErrors>
 </worksheet>
 </file>